--- a/Result/profitability/6257.xlsx
+++ b/Result/profitability/6257.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.15</v>
       </c>
       <c r="M2" t="n">
-        <v>1.38625</v>
+        <v>1.5775</v>
       </c>
       <c r="N2" t="n">
-        <v>27.24375</v>
+        <v>28.2175</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.315</v>
+        <v>1.425</v>
       </c>
       <c r="N3" t="n">
-        <v>26.9275</v>
+        <v>27.94375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>1.17875</v>
+        <v>1.30125</v>
       </c>
       <c r="N4" t="n">
-        <v>27.2</v>
+        <v>27.92</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.96875</v>
+        <v>1.2</v>
       </c>
       <c r="N5" t="n">
-        <v>24.24375</v>
+        <v>24.59375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.87375</v>
+        <v>0.9825</v>
       </c>
       <c r="N6" t="n">
-        <v>21.02625</v>
+        <v>21.90375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.48</v>
       </c>
       <c r="M7" t="n">
-        <v>0.72375</v>
+        <v>0.7675</v>
       </c>
       <c r="N7" t="n">
-        <v>21.34375</v>
+        <v>21.91</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0.51125</v>
+        <v>0.5674999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>21.405</v>
+        <v>21.7275</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5881</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3867</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1508</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>25.64%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>68</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1576</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1220</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.68625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.41375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4499999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2142857142857142</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.580000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08149084017687946</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.642857142857143</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.800000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08905852417302795</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
